--- a/scripts/python/sf-doc-mcp/設計書テンプレート.xlsx
+++ b/scripts/python/sf-doc-mcp/設計書テンプレート.xlsx
@@ -214,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -241,6 +241,10 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1398,10 +1402,10 @@
   </sheetData>
   <mergeCells count="173">
     <mergeCell ref="D20:E20"/>
+    <mergeCell ref="AD17:AE17"/>
+    <mergeCell ref="R24:W24"/>
     <mergeCell ref="AA5:AC5"/>
-    <mergeCell ref="AD17:AE17"/>
     <mergeCell ref="L15:Q15"/>
-    <mergeCell ref="R24:W24"/>
     <mergeCell ref="X18:Z18"/>
     <mergeCell ref="L18:Q18"/>
     <mergeCell ref="B3:F3"/>
@@ -1439,8 +1443,8 @@
     <mergeCell ref="X7:Z7"/>
     <mergeCell ref="L12:Q12"/>
     <mergeCell ref="F15:K15"/>
+    <mergeCell ref="AD18:AE18"/>
     <mergeCell ref="X16:Z16"/>
-    <mergeCell ref="AD18:AE18"/>
     <mergeCell ref="F24:K24"/>
     <mergeCell ref="R6:W6"/>
     <mergeCell ref="B16:C16"/>
@@ -1970,33 +1974,29 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>処理タイトル</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>処理詳細</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="n"/>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
-      <c r="O4" s="3" t="n"/>
-      <c r="P4" s="4" t="n"/>
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>処理内容</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="13" t="n"/>
+      <c r="G4" s="13" t="n"/>
+      <c r="H4" s="13" t="n"/>
+      <c r="I4" s="13" t="n"/>
+      <c r="J4" s="13" t="n"/>
+      <c r="K4" s="13" t="n"/>
+      <c r="L4" s="13" t="n"/>
+      <c r="M4" s="13" t="n"/>
+      <c r="N4" s="13" t="n"/>
+      <c r="O4" s="13" t="n"/>
+      <c r="P4" s="13" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1"/>
     <row r="6" ht="22" customHeight="1"/>
@@ -2029,13 +2029,12 @@
     <row r="33" ht="22" customHeight="1"/>
     <row r="34" ht="22" customHeight="1"/>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="5">
     <mergeCell ref="B1:AE1"/>
+    <mergeCell ref="D4:P4"/>
     <mergeCell ref="B3:P3"/>
-    <mergeCell ref="H4:P4"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="R3:AE3"/>
-    <mergeCell ref="D4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
